--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/122.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/122.xlsx
@@ -426,13 +426,13 @@
         <v>-19.93188590123204</v>
       </c>
       <c r="E2">
-        <v>-5.791739193557683</v>
+        <v>-5.303778005335171</v>
       </c>
       <c r="F2">
-        <v>-2.017874786068755</v>
+        <v>-2.598092371190559</v>
       </c>
       <c r="G2">
-        <v>-7.903249963842742</v>
+        <v>-8.068869936081402</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-19.99164083755468</v>
       </c>
       <c r="E3">
-        <v>-5.91920215145158</v>
+        <v>-7.49550961183354</v>
       </c>
       <c r="F3">
-        <v>-1.821340841227508</v>
+        <v>-2.634748036456363</v>
       </c>
       <c r="G3">
-        <v>-7.342443549490203</v>
+        <v>-7.813338857541676</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-20.04830802053099</v>
       </c>
       <c r="E4">
-        <v>-7.788701132986149</v>
+        <v>-5.561588559065852</v>
       </c>
       <c r="F4">
-        <v>-1.782562218182058</v>
+        <v>-2.297775802151692</v>
       </c>
       <c r="G4">
-        <v>-6.896678592627338</v>
+        <v>-8.042776216140865</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-20.03473391880928</v>
       </c>
       <c r="E5">
-        <v>-7.064158877180915</v>
+        <v>-7.883146986890122</v>
       </c>
       <c r="F5">
-        <v>-1.816337122387677</v>
+        <v>-2.4257598282961</v>
       </c>
       <c r="G5">
-        <v>-7.283237753065878</v>
+        <v>-8.390224591578455</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-19.90124035907308</v>
       </c>
       <c r="E6">
-        <v>-7.912111106643182</v>
+        <v>-7.35996332783595</v>
       </c>
       <c r="F6">
-        <v>-1.304132579657378</v>
+        <v>-1.997141700076779</v>
       </c>
       <c r="G6">
-        <v>-7.320027845643798</v>
+        <v>-7.88549881866117</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-19.60583442571546</v>
       </c>
       <c r="E7">
-        <v>-9.342877940892624</v>
+        <v>-9.761055344656935</v>
       </c>
       <c r="F7">
-        <v>-1.101235304447896</v>
+        <v>-1.641356623202604</v>
       </c>
       <c r="G7">
-        <v>-7.182961328681353</v>
+        <v>-6.861513977909199</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-19.09903816992284</v>
       </c>
       <c r="E8">
-        <v>-9.521965502473963</v>
+        <v>-10.63258733827714</v>
       </c>
       <c r="F8">
-        <v>-1.300769580145942</v>
+        <v>-1.682427660560653</v>
       </c>
       <c r="G8">
-        <v>-6.858428549466598</v>
+        <v>-7.343052689869429</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-18.37550883307508</v>
       </c>
       <c r="E9">
-        <v>-10.8926892998557</v>
+        <v>-10.60790715493534</v>
       </c>
       <c r="F9">
-        <v>-1.104443892632576</v>
+        <v>-1.06347579615903</v>
       </c>
       <c r="G9">
-        <v>-6.184689495132901</v>
+        <v>-7.72047805516512</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-17.43530285325667</v>
       </c>
       <c r="E10">
-        <v>-11.52278570175696</v>
+        <v>-12.70117615108493</v>
       </c>
       <c r="F10">
-        <v>-1.003394744845004</v>
+        <v>-1.110239464430126</v>
       </c>
       <c r="G10">
-        <v>-5.975900009062147</v>
+        <v>-5.654161330282537</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.31220726191179</v>
       </c>
       <c r="E11">
-        <v>-11.93133104130696</v>
+        <v>-12.6086458416862</v>
       </c>
       <c r="F11">
-        <v>-1.010285449283081</v>
+        <v>-1.551659479416902</v>
       </c>
       <c r="G11">
-        <v>-5.10038320410987</v>
+        <v>-6.160873430523385</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.0744173381602</v>
       </c>
       <c r="E12">
-        <v>-12.54008927368408</v>
+        <v>-12.56859601756237</v>
       </c>
       <c r="F12">
-        <v>-1.048855023147693</v>
+        <v>-1.312028937351759</v>
       </c>
       <c r="G12">
-        <v>-3.982693371868828</v>
+        <v>-5.724666018632395</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-13.7873605050312</v>
       </c>
       <c r="E13">
-        <v>-13.40435759499598</v>
+        <v>-13.35540931944707</v>
       </c>
       <c r="F13">
-        <v>-1.104889705847772</v>
+        <v>-1.070801227870896</v>
       </c>
       <c r="G13">
-        <v>-4.011875830797504</v>
+        <v>-5.232735504224393</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.55614701020124</v>
       </c>
       <c r="E14">
-        <v>-14.72468853362037</v>
+        <v>-14.81908457431026</v>
       </c>
       <c r="F14">
-        <v>-1.054497767324404</v>
+        <v>-0.5899532704133397</v>
       </c>
       <c r="G14">
-        <v>-2.933945650483109</v>
+        <v>-3.79808411041691</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.45690061190823</v>
       </c>
       <c r="E15">
-        <v>-15.08922616276382</v>
+        <v>-15.78335518713354</v>
       </c>
       <c r="F15">
-        <v>-1.282360582584874</v>
+        <v>-0.7942347045929163</v>
       </c>
       <c r="G15">
-        <v>-2.57763825518243</v>
+        <v>-3.692239348435332</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.55315865501113</v>
       </c>
       <c r="E16">
-        <v>-15.22144854683978</v>
+        <v>-16.31274285557823</v>
       </c>
       <c r="F16">
-        <v>-0.7363930134433213</v>
+        <v>-0.8531327275881093</v>
       </c>
       <c r="G16">
-        <v>-1.365534974706913</v>
+        <v>-3.312162236162685</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.876842476892408</v>
       </c>
       <c r="E17">
-        <v>-15.9194720588561</v>
+        <v>-16.96532313092757</v>
       </c>
       <c r="F17">
-        <v>-0.8161207284913318</v>
+        <v>-0.366149493414141</v>
       </c>
       <c r="G17">
-        <v>-0.9832431074684943</v>
+        <v>-2.404476860205311</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.409286373331403</v>
       </c>
       <c r="E18">
-        <v>-17.63673280120081</v>
+        <v>-17.39287447588776</v>
       </c>
       <c r="F18">
-        <v>-0.4103538929258869</v>
+        <v>-0.3665953066293372</v>
       </c>
       <c r="G18">
-        <v>-0.5977035950560504</v>
+        <v>-1.58949006989307</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.13351112641643</v>
       </c>
       <c r="E19">
-        <v>-18.60709874003842</v>
+        <v>-18.28638315386719</v>
       </c>
       <c r="F19">
-        <v>-0.2677641389763385</v>
+        <v>-0.007722795073012117</v>
       </c>
       <c r="G19">
-        <v>0.1575973697286709</v>
+        <v>-0.508924695329415</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.995791286846568</v>
       </c>
       <c r="E20">
-        <v>-19.69154599607726</v>
+        <v>-20.00788707635708</v>
       </c>
       <c r="F20">
-        <v>-0.3339994714777625</v>
+        <v>0.2738244833090243</v>
       </c>
       <c r="G20">
-        <v>0.542699890129931</v>
+        <v>-1.106968125907676</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.955522169890978</v>
       </c>
       <c r="E21">
-        <v>-19.72393817065413</v>
+        <v>-19.95133096447529</v>
       </c>
       <c r="F21">
-        <v>-0.2492704131487944</v>
+        <v>0.4514173054016153</v>
       </c>
       <c r="G21">
-        <v>1.583131521121001</v>
+        <v>-0.1821937138765844</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.971113626471594</v>
       </c>
       <c r="E22">
-        <v>-20.04239857676954</v>
+        <v>-21.44459074003058</v>
       </c>
       <c r="F22">
-        <v>0.01608980707153541</v>
+        <v>0.7257824774571338</v>
       </c>
       <c r="G22">
-        <v>0.642936587967984</v>
+        <v>-0.1935323323485882</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.996810383131258</v>
       </c>
       <c r="E23">
-        <v>-20.43836381552623</v>
+        <v>-20.10096985958475</v>
       </c>
       <c r="F23">
-        <v>0.4611705582818491</v>
+        <v>0.3968816003505002</v>
       </c>
       <c r="G23">
-        <v>1.696173409104955</v>
+        <v>-0.6065791676468364</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.015656083695188</v>
       </c>
       <c r="E24">
-        <v>-20.56645623130719</v>
+        <v>-20.38039934822805</v>
       </c>
       <c r="F24">
-        <v>0.4281526655038098</v>
+        <v>0.8137383365888098</v>
       </c>
       <c r="G24">
-        <v>1.469831410584984</v>
+        <v>0.1848828860633441</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.004437051544034</v>
       </c>
       <c r="E25">
-        <v>-21.16519747917934</v>
+        <v>-21.49189065104069</v>
       </c>
       <c r="F25">
-        <v>0.5466399991262852</v>
+        <v>0.7985981080372087</v>
       </c>
       <c r="G25">
-        <v>1.396459789798117</v>
+        <v>-0.1282252004953855</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.970913567675099</v>
       </c>
       <c r="E26">
-        <v>-21.46679384809019</v>
+        <v>-21.55009965593529</v>
       </c>
       <c r="F26">
-        <v>0.0399649655997428</v>
+        <v>0.5949572829004274</v>
       </c>
       <c r="G26">
-        <v>1.786064652132786</v>
+        <v>0.2722746672090249</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.923463439339709</v>
       </c>
       <c r="E27">
-        <v>-21.69065443218537</v>
+        <v>-22.39179353431896</v>
       </c>
       <c r="F27">
-        <v>0.251607464874282</v>
+        <v>0.6851303303137186</v>
       </c>
       <c r="G27">
-        <v>1.27716428129048</v>
+        <v>-0.4629643916077131</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.874230992878694</v>
       </c>
       <c r="E28">
-        <v>-21.89789098819838</v>
+        <v>-22.89270615820341</v>
       </c>
       <c r="F28">
-        <v>0.3749401467450444</v>
+        <v>0.9429101421697974</v>
       </c>
       <c r="G28">
-        <v>1.100854557505514</v>
+        <v>-0.1548320549945081</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.844977716838208</v>
       </c>
       <c r="E29">
-        <v>-21.58796675558743</v>
+        <v>-22.6160480956528</v>
       </c>
       <c r="F29">
-        <v>0.5601046668193514</v>
+        <v>0.8514875507892244</v>
       </c>
       <c r="G29">
-        <v>0.880435124955299</v>
+        <v>-0.6444617402527166</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.838893471257203</v>
       </c>
       <c r="E30">
-        <v>-21.17563108329301</v>
+        <v>-21.12210904899636</v>
       </c>
       <c r="F30">
-        <v>0.5016136562444263</v>
+        <v>0.3729605143507451</v>
       </c>
       <c r="G30">
-        <v>0.7044399029965641</v>
+        <v>-1.077805530252236</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.870558195518447</v>
       </c>
       <c r="E31">
-        <v>-21.76018462209914</v>
+        <v>-21.76410175211577</v>
       </c>
       <c r="F31">
-        <v>0.3892956490155453</v>
+        <v>0.4664427152743471</v>
       </c>
       <c r="G31">
-        <v>0.3776195368141733</v>
+        <v>-1.698546061047741</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.937044097846822</v>
       </c>
       <c r="E32">
-        <v>-20.22320695847379</v>
+        <v>-20.66521319246646</v>
       </c>
       <c r="F32">
-        <v>0.5232637079614413</v>
+        <v>0.8387957315828927</v>
       </c>
       <c r="G32">
-        <v>-0.1869973154540669</v>
+        <v>-0.849053454579676</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.031755979601652</v>
       </c>
       <c r="E33">
-        <v>-20.90562534905968</v>
+        <v>-19.95799234974057</v>
       </c>
       <c r="F33">
-        <v>0.6684079795525935</v>
+        <v>0.7987881527470614</v>
       </c>
       <c r="G33">
-        <v>-0.6429587525778875</v>
+        <v>-0.4596041878853528</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.14969261036881</v>
       </c>
       <c r="E34">
-        <v>-20.26661238183731</v>
+        <v>-20.31813735909659</v>
       </c>
       <c r="F34">
-        <v>0.7421579966227776</v>
+        <v>0.744346678197915</v>
       </c>
       <c r="G34">
-        <v>-0.4380525364246974</v>
+        <v>-1.019698834946949</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.271406893813769</v>
       </c>
       <c r="E35">
-        <v>-20.09970641533661</v>
+        <v>-20.23671086796466</v>
       </c>
       <c r="F35">
-        <v>0.6389367961721808</v>
+        <v>0.6889359756285196</v>
       </c>
       <c r="G35">
-        <v>-1.060471513808612</v>
+        <v>-2.035490075489223</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.394558577110191</v>
       </c>
       <c r="E36">
-        <v>-18.80287372833802</v>
+        <v>-19.06789814116292</v>
       </c>
       <c r="F36">
-        <v>0.8322423565048043</v>
+        <v>1.113239297081225</v>
       </c>
       <c r="G36">
-        <v>-1.723408258047668</v>
+        <v>-2.670932739024631</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.505184591438836</v>
       </c>
       <c r="E37">
-        <v>-18.5128611959388</v>
+        <v>-18.9666324054034</v>
       </c>
       <c r="F37">
-        <v>0.7153015117087554</v>
+        <v>1.32478598214788</v>
       </c>
       <c r="G37">
-        <v>-1.292037553189554</v>
+        <v>-2.002758711742449</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.599467408537013</v>
       </c>
       <c r="E38">
-        <v>-17.78678378744496</v>
+        <v>-19.91734929552173</v>
       </c>
       <c r="F38">
-        <v>1.044189719168066</v>
+        <v>0.9941636167111643</v>
       </c>
       <c r="G38">
-        <v>-1.866850885718749</v>
+        <v>-2.878063641780212</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.679727624664922</v>
       </c>
       <c r="E39">
-        <v>-17.56166428757566</v>
+        <v>-18.81413151472109</v>
       </c>
       <c r="F39">
-        <v>1.175878033448686</v>
+        <v>1.423816696746225</v>
       </c>
       <c r="G39">
-        <v>-2.254317135635049</v>
+        <v>-2.864874428351755</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.741319492887891</v>
       </c>
       <c r="E40">
-        <v>-18.07528380952563</v>
+        <v>-17.94887598607552</v>
       </c>
       <c r="F40">
-        <v>1.215160274975247</v>
+        <v>1.379514107467722</v>
       </c>
       <c r="G40">
-        <v>-1.743668796748007</v>
+        <v>-1.83559271473695</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.799685813165254</v>
       </c>
       <c r="E41">
-        <v>-16.68238407492833</v>
+        <v>-17.21181249963907</v>
       </c>
       <c r="F41">
-        <v>1.441064837871276</v>
+        <v>1.328479184342685</v>
       </c>
       <c r="G41">
-        <v>-1.949528450016508</v>
+        <v>-2.924725781156239</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.856680611781604</v>
       </c>
       <c r="E42">
-        <v>-16.86298414682823</v>
+        <v>-16.30657960245378</v>
       </c>
       <c r="F42">
-        <v>1.269456048580172</v>
+        <v>1.050947392309246</v>
       </c>
       <c r="G42">
-        <v>-2.512738320430558</v>
+        <v>-1.818361325205044</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.924786145239061</v>
       </c>
       <c r="E43">
-        <v>-14.73506326757194</v>
+        <v>-16.35846232915966</v>
       </c>
       <c r="F43">
-        <v>1.118020505239937</v>
+        <v>1.350031838145901</v>
       </c>
       <c r="G43">
-        <v>-1.966402300630173</v>
+        <v>-2.553888401483698</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.01656852200648</v>
       </c>
       <c r="E44">
-        <v>-13.24299900915467</v>
+        <v>-15.22661553568254</v>
       </c>
       <c r="F44">
-        <v>1.507116460486509</v>
+        <v>0.748804810349877</v>
       </c>
       <c r="G44">
-        <v>-2.142622639685578</v>
+        <v>-3.243031424211624</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.13352616444135</v>
       </c>
       <c r="E45">
-        <v>-14.50965394536614</v>
+        <v>-14.29287136614495</v>
       </c>
       <c r="F45">
-        <v>1.674906934815487</v>
+        <v>1.211503498016497</v>
       </c>
       <c r="G45">
-        <v>-1.827203792340437</v>
+        <v>-2.110881129055046</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.29378456024993</v>
       </c>
       <c r="E46">
-        <v>-14.02735334965322</v>
+        <v>-14.46110417552991</v>
       </c>
       <c r="F46">
-        <v>1.464334228886828</v>
+        <v>1.138694202260084</v>
       </c>
       <c r="G46">
-        <v>-1.339189653305393</v>
+        <v>-2.78540478268155</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.49325585090824</v>
       </c>
       <c r="E47">
-        <v>-13.96165424874994</v>
+        <v>-14.14824096328798</v>
       </c>
       <c r="F47">
-        <v>1.570014924624102</v>
+        <v>1.085215620907524</v>
       </c>
       <c r="G47">
-        <v>-2.255578453485511</v>
+        <v>-2.943923634738473</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.73942118846721</v>
       </c>
       <c r="E48">
-        <v>-12.21435160983834</v>
+        <v>-13.57331948869617</v>
       </c>
       <c r="F48">
-        <v>1.491803607990125</v>
+        <v>1.094283920979331</v>
       </c>
       <c r="G48">
-        <v>-2.113748061492055</v>
+        <v>-2.551415423965863</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.03193396873437</v>
       </c>
       <c r="E49">
-        <v>-11.44159469127344</v>
+        <v>-12.13848155631383</v>
       </c>
       <c r="F49">
-        <v>1.395734423453652</v>
+        <v>1.126339712413741</v>
       </c>
       <c r="G49">
-        <v>-1.172957230141969</v>
+        <v>-2.280645904308872</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.36164930459518</v>
       </c>
       <c r="E50">
-        <v>-11.7923204746935</v>
+        <v>-11.14618421785707</v>
       </c>
       <c r="F50">
-        <v>1.364736547570756</v>
+        <v>0.8514653789064083</v>
       </c>
       <c r="G50">
-        <v>-1.986851540426251</v>
+        <v>-2.191294280203943</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.73613814083078</v>
       </c>
       <c r="E51">
-        <v>-9.823865279143323</v>
+        <v>-11.40247773279519</v>
       </c>
       <c r="F51">
-        <v>1.625340107074063</v>
+        <v>1.026125969496563</v>
       </c>
       <c r="G51">
-        <v>-1.466927052938172</v>
+        <v>-1.960863757942972</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.13967123717211</v>
       </c>
       <c r="E52">
-        <v>-11.09148025184442</v>
+        <v>-11.04032660945377</v>
       </c>
       <c r="F52">
-        <v>1.352345632488358</v>
+        <v>1.391810000195193</v>
       </c>
       <c r="G52">
-        <v>-1.842372712001378</v>
+        <v>-1.584514319947545</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-12.5770934939467</v>
       </c>
       <c r="E53">
-        <v>-9.738648455266981</v>
+        <v>-11.29481779173683</v>
       </c>
       <c r="F53">
-        <v>1.6368425631379</v>
+        <v>1.125414828159124</v>
       </c>
       <c r="G53">
-        <v>-1.886363241127213</v>
+        <v>-1.186901247953379</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-13.04201810958081</v>
       </c>
       <c r="E54">
-        <v>-8.245945682014632</v>
+        <v>-11.17297014161245</v>
       </c>
       <c r="F54">
-        <v>1.485528965153154</v>
+        <v>1.355139289723193</v>
       </c>
       <c r="G54">
-        <v>-1.890200163407229</v>
+        <v>-2.886068540894169</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-13.52589092711221</v>
       </c>
       <c r="E55">
-        <v>-8.65987537715975</v>
+        <v>-9.577018160985212</v>
       </c>
       <c r="F55">
-        <v>1.466085807629304</v>
+        <v>1.094771702401286</v>
       </c>
       <c r="G55">
-        <v>-1.737620430047759</v>
+        <v>-1.26525192923131</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-14.0349985341516</v>
       </c>
       <c r="E56">
-        <v>-8.089020472226832</v>
+        <v>-9.545269029717435</v>
       </c>
       <c r="F56">
-        <v>1.53025757132291</v>
+        <v>1.227513181115674</v>
       </c>
       <c r="G56">
-        <v>-2.599911605570647</v>
+        <v>-1.599967946524863</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-14.55054649337639</v>
       </c>
       <c r="E57">
-        <v>-7.878437373922145</v>
+        <v>-9.207028249136521</v>
       </c>
       <c r="F57">
-        <v>1.871555698335603</v>
+        <v>1.045851026673362</v>
       </c>
       <c r="G57">
-        <v>-1.874872337560403</v>
+        <v>-1.580816440580179</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-15.07842411143595</v>
       </c>
       <c r="E58">
-        <v>-8.131755681437216</v>
+        <v>-8.650786729826354</v>
       </c>
       <c r="F58">
-        <v>1.633253885533514</v>
+        <v>1.175596133795738</v>
       </c>
       <c r="G58">
-        <v>-2.752375469836242</v>
+        <v>-3.018781690472473</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-15.60612792316395</v>
       </c>
       <c r="E59">
-        <v>-7.659707550877659</v>
+        <v>-8.430802519481745</v>
       </c>
       <c r="F59">
-        <v>1.910099932905569</v>
+        <v>1.184026200383622</v>
       </c>
       <c r="G59">
-        <v>-2.285363431702334</v>
+        <v>-2.887376206382181</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-16.12256652104256</v>
       </c>
       <c r="E60">
-        <v>-7.455405446021611</v>
+        <v>-7.907301867247035</v>
       </c>
       <c r="F60">
-        <v>1.629593941162934</v>
+        <v>1.204010985330553</v>
       </c>
       <c r="G60">
-        <v>-2.773579514015274</v>
+        <v>-1.966412232266791</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-16.62785764963233</v>
       </c>
       <c r="E61">
-        <v>-7.919238924731254</v>
+        <v>-8.214599584933538</v>
       </c>
       <c r="F61">
-        <v>1.547538970272185</v>
+        <v>0.9995941442952061</v>
       </c>
       <c r="G61">
-        <v>-2.830487791835345</v>
+        <v>-2.337219817029478</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-17.09765939071641</v>
       </c>
       <c r="E62">
-        <v>-6.092275899550733</v>
+        <v>-8.359130361362345</v>
       </c>
       <c r="F62">
-        <v>1.735369659255134</v>
+        <v>1.212494897919562</v>
       </c>
       <c r="G62">
-        <v>-3.301442689706525</v>
+        <v>-2.963502201057723</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-17.53617770401876</v>
       </c>
       <c r="E63">
-        <v>-7.034230192464221</v>
+        <v>-7.839768734370647</v>
       </c>
       <c r="F63">
-        <v>1.601489495987545</v>
+        <v>1.250590943715458</v>
       </c>
       <c r="G63">
-        <v>-3.081384106620091</v>
+        <v>-4.34426122403141</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-17.92795653830091</v>
       </c>
       <c r="E64">
-        <v>-5.863221155768759</v>
+        <v>-6.675353155830353</v>
       </c>
       <c r="F64">
-        <v>1.666651075878301</v>
+        <v>0.8870179930021085</v>
       </c>
       <c r="G64">
-        <v>-2.771387932868276</v>
+        <v>-3.718372794922339</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-18.26416172767636</v>
       </c>
       <c r="E65">
-        <v>-5.78377360777819</v>
+        <v>-6.739399363720835</v>
       </c>
       <c r="F65">
-        <v>1.426038636145586</v>
+        <v>1.058194430578297</v>
       </c>
       <c r="G65">
-        <v>-3.583749460567875</v>
+        <v>-3.908941038344945</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-18.54670718331548</v>
       </c>
       <c r="E66">
-        <v>-5.566343456773906</v>
+        <v>-6.645265974523391</v>
       </c>
       <c r="F66">
-        <v>1.5590699330425</v>
+        <v>1.208953731492639</v>
       </c>
       <c r="G66">
-        <v>-3.889620694577758</v>
+        <v>-3.689528011638669</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-18.75763810734066</v>
       </c>
       <c r="E67">
-        <v>-5.542922189206235</v>
+        <v>-5.221821682744353</v>
       </c>
       <c r="F67">
-        <v>1.439688597430759</v>
+        <v>0.8449515964762059</v>
       </c>
       <c r="G67">
-        <v>-4.332641209188568</v>
+        <v>-4.722805553719374</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-18.90852569966403</v>
       </c>
       <c r="E68">
-        <v>-5.895155954470851</v>
+        <v>-5.823977400018288</v>
       </c>
       <c r="F68">
-        <v>1.065189659606793</v>
+        <v>0.3786539371167499</v>
       </c>
       <c r="G68">
-        <v>-4.317713959351994</v>
+        <v>-3.809581635074799</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-18.9914736161138</v>
       </c>
       <c r="E69">
-        <v>-6.202485371475407</v>
+        <v>-7.297465858056092</v>
       </c>
       <c r="F69">
-        <v>0.9463673721832018</v>
+        <v>0.8127120951556051</v>
       </c>
       <c r="G69">
-        <v>-4.280543154037058</v>
+        <v>-3.827739977357701</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-19.00840003431378</v>
       </c>
       <c r="E70">
-        <v>-5.570052276986187</v>
+        <v>-5.42033186934459</v>
       </c>
       <c r="F70">
-        <v>1.129252147592234</v>
+        <v>0.6629616149093972</v>
       </c>
       <c r="G70">
-        <v>-3.983487902798254</v>
+        <v>-3.12726495724885</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-18.97022968045813</v>
       </c>
       <c r="E71">
-        <v>-5.916290342664648</v>
+        <v>-6.165125460912126</v>
       </c>
       <c r="F71">
-        <v>0.658139230396884</v>
+        <v>0.4367608990071809</v>
       </c>
       <c r="G71">
-        <v>-3.464970397164365</v>
+        <v>-3.833473842231719</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-18.86846583521282</v>
       </c>
       <c r="E72">
-        <v>-6.15922938775414</v>
+        <v>-6.827564224176169</v>
       </c>
       <c r="F72">
-        <v>0.4527998806657939</v>
+        <v>0.002676609820721015</v>
       </c>
       <c r="G72">
-        <v>-4.168957906090383</v>
+        <v>-3.44614001413699</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-18.72410585097217</v>
       </c>
       <c r="E73">
-        <v>-5.838984762879707</v>
+        <v>-5.824846867027761</v>
       </c>
       <c r="F73">
-        <v>0.8415038686982942</v>
+        <v>0.6638247346333117</v>
       </c>
       <c r="G73">
-        <v>-3.454353477619922</v>
+        <v>-3.38400107436487</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-18.53591619466207</v>
       </c>
       <c r="E74">
-        <v>-5.696931061733096</v>
+        <v>-7.004962664952648</v>
       </c>
       <c r="F74">
-        <v>0.6637075403955691</v>
+        <v>0.5938882814075057</v>
       </c>
       <c r="G74">
-        <v>-3.430693008650751</v>
+        <v>-2.976999295221331</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-18.31463804150686</v>
       </c>
       <c r="E75">
-        <v>-7.113496601494483</v>
+        <v>-8.3224406649522</v>
       </c>
       <c r="F75">
-        <v>0.9911482406481675</v>
+        <v>0.03482663175709952</v>
       </c>
       <c r="G75">
-        <v>-3.407151719320993</v>
+        <v>-2.815888286007159</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-18.07684374679997</v>
       </c>
       <c r="E76">
-        <v>-6.83541659810547</v>
+        <v>-7.66378770595857</v>
       </c>
       <c r="F76">
-        <v>0.4825086199335225</v>
+        <v>-0.1690074055013654</v>
       </c>
       <c r="G76">
-        <v>-3.302230599544872</v>
+        <v>-4.097446811896586</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-17.81882814369758</v>
       </c>
       <c r="E77">
-        <v>-7.427894966425013</v>
+        <v>-8.58693977479221</v>
       </c>
       <c r="F77">
-        <v>0.1612491238688843</v>
+        <v>0.2509621047137404</v>
       </c>
       <c r="G77">
-        <v>-3.056336519069965</v>
+        <v>-3.985735763219419</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-17.56666800986091</v>
       </c>
       <c r="E78">
-        <v>-7.166063127775521</v>
+        <v>-8.630435767635884</v>
       </c>
       <c r="F78">
-        <v>0.4837716254010855</v>
+        <v>0.02063583490180435</v>
       </c>
       <c r="G78">
-        <v>-3.098347341963316</v>
+        <v>-2.685197879753351</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-17.31788488012684</v>
       </c>
       <c r="E79">
-        <v>-7.947469431695072</v>
+        <v>-9.938965502996281</v>
       </c>
       <c r="F79">
-        <v>-0.07108211763199809</v>
+        <v>-0.2741924012871072</v>
       </c>
       <c r="G79">
-        <v>-3.74793596658803</v>
+        <v>-2.90033037107735</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-17.08288396353847</v>
       </c>
       <c r="E80">
-        <v>-8.744553312629177</v>
+        <v>-10.11921688239759</v>
       </c>
       <c r="F80">
-        <v>0.2469790843364102</v>
+        <v>0.004297532825173289</v>
       </c>
       <c r="G80">
-        <v>-2.045709729568953</v>
+        <v>-2.288011868133751</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-16.8706827527196</v>
       </c>
       <c r="E81">
-        <v>-10.0830887167644</v>
+        <v>-10.99981035250715</v>
       </c>
       <c r="F81">
-        <v>0.3057187367400593</v>
+        <v>-0.666132692357808</v>
       </c>
       <c r="G81">
-        <v>-2.663881277025983</v>
+        <v>-1.77490710445657</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-16.67000755750156</v>
       </c>
       <c r="E82">
-        <v>-10.06800889831885</v>
+        <v>-10.28501790124043</v>
       </c>
       <c r="F82">
-        <v>0.1392554079682189</v>
+        <v>-0.2132506058080396</v>
       </c>
       <c r="G82">
-        <v>-2.391648496240635</v>
+        <v>-2.618967105694691</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-16.49741213845297</v>
       </c>
       <c r="E83">
-        <v>-11.38505216481367</v>
+        <v>-12.34092245835273</v>
       </c>
       <c r="F83">
-        <v>0.04356948026328299</v>
+        <v>-0.4106706341089748</v>
       </c>
       <c r="G83">
-        <v>-2.365064815560288</v>
+        <v>-1.5053194495571</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-16.33810476019888</v>
       </c>
       <c r="E84">
-        <v>-12.18717623731831</v>
+        <v>-12.39202628752929</v>
       </c>
       <c r="F84">
-        <v>-0.1304908857849204</v>
+        <v>-0.7832984233938491</v>
       </c>
       <c r="G84">
-        <v>-1.510083324588111</v>
+        <v>-2.011630973787696</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-16.19661249539715</v>
       </c>
       <c r="E85">
-        <v>-12.61778883070769</v>
+        <v>-14.54332767808718</v>
       </c>
       <c r="F85">
-        <v>-0.3157821023324626</v>
+        <v>-0.8266294090932302</v>
       </c>
       <c r="G85">
-        <v>-1.944208403334899</v>
+        <v>-1.02482686998728</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-16.07266368432299</v>
       </c>
       <c r="E86">
-        <v>-14.16134183859217</v>
+        <v>-14.17613183470122</v>
       </c>
       <c r="F86">
-        <v>0.009921272530898766</v>
+        <v>-0.8482620400451754</v>
       </c>
       <c r="G86">
-        <v>-1.571632987254241</v>
+        <v>-1.562164827011925</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-15.95522606046985</v>
       </c>
       <c r="E87">
-        <v>-15.85537603775153</v>
+        <v>-17.71919631288048</v>
       </c>
       <c r="F87">
-        <v>-0.8583613326679327</v>
+        <v>-1.00354915617176</v>
       </c>
       <c r="G87">
-        <v>-1.560843919341756</v>
+        <v>-1.505928589936326</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-15.86033958037669</v>
       </c>
       <c r="E88">
-        <v>-17.39571835756458</v>
+        <v>-17.63327304705895</v>
       </c>
       <c r="F88">
-        <v>-0.768689528176878</v>
+        <v>-0.8909745885845772</v>
       </c>
       <c r="G88">
-        <v>-1.160337430546267</v>
+        <v>-0.9149300002656333</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-15.77646895440605</v>
       </c>
       <c r="E89">
-        <v>-17.92020621713295</v>
+        <v>-19.52642424833558</v>
       </c>
       <c r="F89">
-        <v>-0.9693624884281258</v>
+        <v>-0.9675222221543852</v>
       </c>
       <c r="G89">
-        <v>-1.170858344270071</v>
+        <v>-1.173738518889237</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-15.71901948030759</v>
       </c>
       <c r="E90">
-        <v>-19.31420184244011</v>
+        <v>-21.01659107614363</v>
       </c>
       <c r="F90">
-        <v>-0.8394091239778688</v>
+        <v>-1.113633346206913</v>
       </c>
       <c r="G90">
-        <v>-0.9058591054880303</v>
+        <v>-0.4663411480577697</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-15.69236886673733</v>
       </c>
       <c r="E91">
-        <v>-21.39653910233519</v>
+        <v>-22.23494078011528</v>
       </c>
       <c r="F91">
-        <v>-1.001259909270992</v>
+        <v>-1.353666941427535</v>
       </c>
       <c r="G91">
-        <v>-1.076113841481669</v>
+        <v>-0.8378174630193895</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-15.69579680313049</v>
       </c>
       <c r="E92">
-        <v>-23.20083258663331</v>
+        <v>-24.43465608628917</v>
       </c>
       <c r="F92">
-        <v>-1.746486981134263</v>
+        <v>-1.767714975224813</v>
       </c>
       <c r="G92">
-        <v>-0.9459266381498295</v>
+        <v>-0.2620705566481196</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-15.7471181177231</v>
       </c>
       <c r="E93">
-        <v>-25.62029662250342</v>
+        <v>-26.56248186759129</v>
       </c>
       <c r="F93">
-        <v>-1.294191657626165</v>
+        <v>-1.991448277310775</v>
       </c>
       <c r="G93">
-        <v>-0.6472094930503117</v>
+        <v>-0.0504538646868268</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-15.8328069306645</v>
       </c>
       <c r="E94">
-        <v>-27.41850383773523</v>
+        <v>-28.31908599211464</v>
       </c>
       <c r="F94">
-        <v>-2.087515878141331</v>
+        <v>-1.866505758376968</v>
       </c>
       <c r="G94">
-        <v>-0.8823145056127336</v>
+        <v>-0.8254029172471227</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-15.96459951682642</v>
       </c>
       <c r="E95">
-        <v>-29.96183975161115</v>
+        <v>-30.54835638389959</v>
       </c>
       <c r="F95">
-        <v>-2.135159295048454</v>
+        <v>-1.927240088381113</v>
       </c>
       <c r="G95">
-        <v>-0.4018219260429135</v>
+        <v>-0.2449682783922447</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-16.132126813634</v>
       </c>
       <c r="E96">
-        <v>-31.9177623953451</v>
+        <v>-32.50079210264764</v>
       </c>
       <c r="F96">
-        <v>-2.065810396717276</v>
+        <v>-2.0687259993076</v>
       </c>
       <c r="G96">
-        <v>-0.5637572610963636</v>
+        <v>-0.3740894860604388</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-16.32021520208605</v>
       </c>
       <c r="E97">
-        <v>-33.92146949680799</v>
+        <v>-36.45892292294795</v>
       </c>
       <c r="F97">
-        <v>-2.603861811840505</v>
+        <v>-2.53465782260059</v>
       </c>
       <c r="G97">
-        <v>-1.143106041014361</v>
+        <v>-2.04708691651329</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-16.52711636022638</v>
       </c>
       <c r="E98">
-        <v>-37.14951068064367</v>
+        <v>-37.02946989164835</v>
       </c>
       <c r="F98">
-        <v>-2.790775535098415</v>
+        <v>-2.439838973884357</v>
       </c>
       <c r="G98">
-        <v>-0.814431769329978</v>
+        <v>-0.8293027398923841</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-16.71992045108845</v>
       </c>
       <c r="E99">
-        <v>-39.56576176420533</v>
+        <v>-40.56775456551252</v>
       </c>
       <c r="F99">
-        <v>-2.869743071307014</v>
+        <v>-2.553754148528959</v>
       </c>
       <c r="G99">
-        <v>-1.689733388822201</v>
+        <v>-2.341351377862488</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-16.90139723393716</v>
       </c>
       <c r="E100">
-        <v>-42.25339523809866</v>
+        <v>-43.30060258813543</v>
       </c>
       <c r="F100">
-        <v>-3.081619167204081</v>
+        <v>-2.865465481629412</v>
       </c>
       <c r="G100">
-        <v>-1.415348753436327</v>
+        <v>-1.655002455569707</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-17.04424946756236</v>
       </c>
       <c r="E101">
-        <v>-44.10199078361382</v>
+        <v>-45.58217006199796</v>
       </c>
       <c r="F101">
-        <v>-3.367827292095255</v>
+        <v>-3.197188522677359</v>
       </c>
       <c r="G101">
-        <v>-1.443120919965273</v>
+        <v>-2.061789049253194</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-17.14937444057165</v>
       </c>
       <c r="E102">
-        <v>-46.03241359021059</v>
+        <v>-47.94268921594723</v>
       </c>
       <c r="F102">
-        <v>-3.395604701999106</v>
+        <v>-3.327900482261112</v>
       </c>
       <c r="G102">
-        <v>-2.432219231824404</v>
+        <v>-2.405840804967491</v>
       </c>
     </row>
   </sheetData>
